--- a/Day3/Normalization.xlsx
+++ b/Day3/Normalization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Corp\Genspark\Pre\2026\Participants\Day3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FC2E8B-646C-453A-AE13-7B5F891940BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E23725-1D5B-4625-9F7F-1B65F04C6152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{80DBF597-1F79-4232-B919-96A6C2CD5DDE}"/>
   </bookViews>
@@ -733,6 +733,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AC55AF-4A8F-48ED-930B-5A3CE1DF4E45}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
